--- a/data/trans_bre/P16A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,91</t>
+          <t>-3,33; 0,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,91</t>
+          <t>-4,59; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,14</t>
+          <t>-0,29; 5,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,15</t>
+          <t>-2,02; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 22,87</t>
+          <t>-51,55; 21,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 22,99</t>
+          <t>-40,31; 25,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 107,03</t>
+          <t>-4,14; 124,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 72,33</t>
+          <t>-26,9; 63,17</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,64</t>
+          <t>-4,21; 0,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,69</t>
+          <t>-2,2; 2,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,25</t>
+          <t>-2,79; 2,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 6,78</t>
+          <t>0,03; 6,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 11,62</t>
+          <t>-47,09; 6,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 44,36</t>
+          <t>-26,23; 41,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 31,3</t>
+          <t>-28,45; 31,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 184,4</t>
+          <t>-1,35; 195,1</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,09</t>
+          <t>-3,33; 2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; -0,17</t>
+          <t>-6,28; 0,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,9</t>
+          <t>-2,29; 2,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,54</t>
+          <t>-5,47; 0,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 36,83</t>
+          <t>-38,62; 40,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,44; -0,76</t>
+          <t>-49,16; 2,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 51,72</t>
+          <t>-28,14; 52,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 7,12</t>
+          <t>-66,66; 15,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,46</t>
+          <t>-1,23; 3,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,71</t>
+          <t>-3,56; 1,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,03</t>
+          <t>-2,41; 2,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,85</t>
+          <t>-2,39; 2,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 56,26</t>
+          <t>-14,94; 59,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 20,26</t>
+          <t>-30,39; 20,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 39,8</t>
+          <t>-22,67; 37,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 44,45</t>
+          <t>-24,71; 42,63</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,73</t>
+          <t>-1,73; 0,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,27</t>
+          <t>-2,67; 0,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,97</t>
+          <t>-0,7; 1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,22</t>
+          <t>-1,03; 2,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 11,55</t>
+          <t>-23,63; 10,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 3,53</t>
+          <t>-25,74; 4,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 28,1</t>
+          <t>-8,72; 28,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 40,2</t>
+          <t>-13,69; 43,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,87</t>
+          <t>-3,67; 0,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,02</t>
+          <t>-4,53; 1,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,61</t>
+          <t>-0,13; 5,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,79</t>
+          <t>-1,86; 2,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 21,41</t>
+          <t>-55,05; 25,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 25,66</t>
+          <t>-37,35; 22,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 124,91</t>
+          <t>-1,6; 122,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,9; 63,17</t>
+          <t>-24,53; 60,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,44</t>
+          <t>-4,23; 0,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,52</t>
+          <t>-2,26; 2,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,3</t>
+          <t>-2,68; 2,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,55</t>
+          <t>-1,81; 3,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,09; 6,66</t>
+          <t>-46,24; 9,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 41,33</t>
+          <t>-25,77; 43,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 31,2</t>
+          <t>-28,36; 30,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 195,1</t>
+          <t>-19,73; 52,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-30,62%</t>
+          <t>-1,57%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,18</t>
+          <t>-3,49; 2,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,21</t>
+          <t>-6,57; -0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,79</t>
+          <t>-2,56; 2,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,75</t>
+          <t>-2,54; 2,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 40,27</t>
+          <t>-40,27; 34,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 2,14</t>
+          <t>-49,18; -0,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 52,62</t>
+          <t>-30,65; 51,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 15,42</t>
+          <t>-31,98; 46,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,6</t>
+          <t>-1,33; 3,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,73</t>
+          <t>-3,75; 1,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,98</t>
+          <t>-2,34; 2,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,84</t>
+          <t>-1,96; 2,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 59,43</t>
+          <t>-15,53; 59,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 20,99</t>
+          <t>-32,37; 19,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 37,9</t>
+          <t>-23,4; 39,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 42,63</t>
+          <t>-20,35; 40,95</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,7</t>
+          <t>-1,73; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,33</t>
+          <t>-2,57; 0,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,98</t>
+          <t>-0,78; 1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,37</t>
+          <t>-0,74; 1,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 10,64</t>
+          <t>-22,35; 11,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 4,07</t>
+          <t>-25,06; 3,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 28,16</t>
+          <t>-8,98; 28,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 43,19</t>
+          <t>-9,44; 29,68</t>
         </is>
       </c>
     </row>
